--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Implantable Device: Transmitter, ResourceType Device</t>
+    <t>This StructureDefinition contains the maps for VistA GENERATOR IMPLANT (file 698) to FHIR Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device</t>
+    <t>http://va.gov/fhir/StructureDefinition/ImplantableDevicePacemakerDevice</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,6 +364,194 @@
     <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
   </si>
   <si>
+    <t>Device.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Device.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>Device.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Device.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>1349: source value from GENERATOR IMPLANT - IEN (#698-.001)</t>
+  </si>
+  <si>
+    <t>Device.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Device.definition</t>
   </si>
   <si>
@@ -399,29 +587,7 @@
     <t>Device.udiCarrier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -461,6 +627,9 @@
   </si>
   <si>
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -567,9 +736,6 @@
     <t>Supports a way to distinguish hand entered from machine read data.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
@@ -603,20 +769,16 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1357: transform using "inactive" on GENERATOR IMPLANT - EXPLANT DATE (#698-96) case is not NULL</t>
+  </si>
+  <si>
     <t>Device.statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
   </si>
   <si>
     <t>Reason for the dtatus of the Device availability.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>The availability status reason of the device.</t>
@@ -647,6 +809,9 @@
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>Device.manufacturer</t>
   </si>
   <si>
@@ -681,6 +846,9 @@
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -696,6 +864,9 @@
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1374: target not supported</t>
+  </si>
+  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -705,6 +876,9 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
+    <t>1377: target not supported</t>
+  </si>
+  <si>
     <t>Device.serialNumber</t>
   </si>
   <si>
@@ -720,6 +894,9 @@
     <t>.playedRole[typeCode=MANU].id</t>
   </si>
   <si>
+    <t>1380: source value from GENERATOR IMPLANT - PACEMAKER SERIAL NUMBER (#698-4)</t>
+  </si>
+  <si>
     <t>Device.deviceName</t>
   </si>
   <si>
@@ -727,6 +904,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -803,10 +983,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>Codes to identify medical devices</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/device-kind</t>
+    <t>http://va.gov/fhir/ValueSet/VFdeviceTypePacemaker</t>
   </si>
   <si>
     <t>1395: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - TRANSMITTER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (#698-12 &gt; 698.4-1)</t>
@@ -964,11 +1141,10 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (#698-1)</t>
+  </si>
+  <si>
     <t>Device.owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Organization responsible for device</t>
@@ -1391,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
@@ -1410,28 +1586,29 @@
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.9765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="1.04296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.40234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="16.3984375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="164.38671875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="164.38671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1547,6 +1724,9 @@
       <c r="AN1" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO1" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1661,6 +1841,9 @@
       <c r="AN2" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO2" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -1773,6 +1956,9 @@
       <c r="AN3" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO3" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -1887,6 +2073,9 @@
       <c r="AN4" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO4" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2001,6 +2190,9 @@
       <c r="AN5" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO5" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2115,6 +2307,9 @@
       <c r="AN6" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO6" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2229,6 +2424,9 @@
       <c r="AN7" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO7" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -2343,6 +2541,9 @@
       <c r="AN8" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO8" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -2459,6 +2660,9 @@
       <c r="AN9" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO9" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -2573,6 +2777,9 @@
       <c r="AN10" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO10" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -2659,7 +2866,7 @@
         <v>37</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>38</v>
@@ -2671,10 +2878,10 @@
         <v>37</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>37</v>
@@ -2683,47 +2890,50 @@
         <v>37</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>117</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2761,19 +2971,19 @@
         <v>37</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>38</v>
@@ -2785,27 +2995,30 @@
         <v>37</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2822,22 +3035,26 @@
         <v>37</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>37</v>
       </c>
@@ -2861,13 +3078,13 @@
         <v>37</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>37</v>
@@ -2885,7 +3102,7 @@
         <v>37</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>38</v>
@@ -2897,10 +3114,10 @@
         <v>37</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>37</v>
@@ -2909,26 +3126,29 @@
         <v>37</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>37</v>
@@ -2937,21 +3157,23 @@
         <v>37</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>37</v>
       </c>
@@ -2975,13 +3197,13 @@
         <v>37</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>37</v>
@@ -2999,22 +3221,22 @@
         <v>37</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>37</v>
@@ -3023,50 +3245,53 @@
         <v>37</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>46</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>37</v>
@@ -3079,7 +3304,7 @@
         <v>37</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>37</v>
@@ -3115,22 +3340,22 @@
         <v>37</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>37</v>
@@ -3139,29 +3364,32 @@
         <v>37</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>45</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>37</v>
@@ -3170,15 +3398,17 @@
         <v>46</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>37</v>
@@ -3191,7 +3421,7 @@
         <v>37</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>37</v>
@@ -3227,7 +3457,7 @@
         <v>37</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>38</v>
@@ -3242,28 +3472,31 @@
         <v>57</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>37</v>
+        <v>157</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>157</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3279,16 +3512,16 @@
         <v>37</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3339,7 +3572,7 @@
         <v>37</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>38</v>
@@ -3354,24 +3587,27 @@
         <v>57</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3391,21 +3627,21 @@
         <v>37</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>37</v>
       </c>
@@ -3453,7 +3689,7 @@
         <v>37</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>38</v>
@@ -3468,7 +3704,7 @@
         <v>57</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>37</v>
@@ -3477,19 +3713,22 @@
         <v>37</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3505,20 +3744,18 @@
         <v>37</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>37</v>
@@ -3567,7 +3804,7 @@
         <v>37</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>38</v>
@@ -3582,28 +3819,31 @@
         <v>57</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3622,16 +3862,16 @@
         <v>46</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3681,13 +3921,13 @@
         <v>37</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>37</v>
@@ -3696,24 +3936,27 @@
         <v>57</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3736,18 +3979,16 @@
         <v>37</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>37</v>
       </c>
@@ -3771,13 +4012,13 @@
         <v>37</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>37</v>
@@ -3795,7 +4036,7 @@
         <v>37</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>38</v>
@@ -3807,10 +4048,10 @@
         <v>37</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>37</v>
@@ -3819,47 +4060,50 @@
         <v>37</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3885,13 +4129,13 @@
         <v>37</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>37</v>
@@ -3909,43 +4153,46 @@
         <v>37</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3958,22 +4205,26 @@
         <v>37</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>37</v>
       </c>
@@ -3997,31 +4248,31 @@
         <v>37</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>38</v>
@@ -4033,18 +4284,21 @@
         <v>37</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>37</v>
       </c>
     </row>
@@ -4061,7 +4315,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>45</v>
@@ -4073,10 +4327,10 @@
         <v>37</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>190</v>
@@ -4084,9 +4338,7 @@
       <c r="M24" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>37</v>
@@ -4150,28 +4402,31 @@
         <v>57</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>194</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>37</v>
+        <v>195</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>37</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4190,13 +4445,13 @@
         <v>37</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4247,7 +4502,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -4262,24 +4517,27 @@
         <v>57</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>199</v>
+        <v>37</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>37</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4293,7 +4551,7 @@
         <v>45</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>37</v>
@@ -4302,16 +4560,18 @@
         <v>37</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>37</v>
       </c>
@@ -4359,7 +4619,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -4374,28 +4634,31 @@
         <v>57</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4405,24 +4668,26 @@
         <v>45</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>37</v>
@@ -4471,7 +4736,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -4486,28 +4751,31 @@
         <v>57</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>37</v>
+        <v>215</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4523,18 +4791,20 @@
         <v>37</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>37</v>
@@ -4583,7 +4853,7 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -4598,24 +4868,27 @@
         <v>57</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4629,7 +4902,7 @@
         <v>45</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>37</v>
@@ -4638,18 +4911,18 @@
         <v>37</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>37</v>
       </c>
@@ -4673,13 +4946,13 @@
         <v>37</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>37</v>
+        <v>224</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>37</v>
@@ -4697,7 +4970,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -4712,24 +4985,27 @@
         <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4740,27 +5016,29 @@
         <v>38</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>37</v>
@@ -4785,13 +5063,13 @@
         <v>37</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>37</v>
+        <v>232</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>37</v>
@@ -4809,13 +5087,13 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>37</v>
@@ -4824,24 +5102,27 @@
         <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>37</v>
+        <v>235</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>235</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4852,7 +5133,7 @@
         <v>38</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>37</v>
@@ -4864,13 +5145,13 @@
         <v>37</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>123</v>
+        <v>238</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4897,13 +5178,13 @@
         <v>37</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>37</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>37</v>
@@ -4921,53 +5202,56 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>37</v>
@@ -4976,16 +5260,16 @@
         <v>37</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>92</v>
+        <v>243</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>94</v>
+        <v>245</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5035,75 +5319,74 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>37</v>
+        <v>247</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>37</v>
+        <v>248</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>248</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>37</v>
       </c>
@@ -5151,53 +5434,56 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>37</v>
+        <v>253</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>45</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>37</v>
@@ -5206,13 +5492,13 @@
         <v>37</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>121</v>
+        <v>255</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5263,10 +5549,10 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>45</v>
@@ -5278,24 +5564,27 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>37</v>
+        <v>258</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>37</v>
+        <v>260</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5303,13 +5592,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>45</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>37</v>
@@ -5318,13 +5607,13 @@
         <v>37</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>65</v>
+        <v>255</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5351,13 +5640,13 @@
         <v>37</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>232</v>
+        <v>37</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>233</v>
+        <v>37</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>37</v>
@@ -5375,10 +5664,10 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>45</v>
@@ -5390,24 +5679,27 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>37</v>
+        <v>265</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>37</v>
+        <v>266</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>266</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5421,7 +5713,7 @@
         <v>45</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>37</v>
@@ -5430,13 +5722,13 @@
         <v>37</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5487,7 +5779,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -5502,24 +5794,27 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>37</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>239</v>
+        <v>270</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>270</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5533,7 +5828,7 @@
         <v>45</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>37</v>
@@ -5542,16 +5837,16 @@
         <v>37</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5601,7 +5896,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -5616,24 +5911,27 @@
         <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>37</v>
+        <v>276</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>276</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5641,13 +5939,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>37</v>
@@ -5656,13 +5954,13 @@
         <v>37</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5689,13 +5987,13 @@
         <v>37</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>246</v>
+        <v>37</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>37</v>
@@ -5713,13 +6011,13 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>37</v>
@@ -5737,15 +6035,18 @@
         <v>37</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>248</v>
+        <v>280</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>280</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5756,7 +6057,7 @@
         <v>38</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>37</v>
@@ -5768,13 +6069,13 @@
         <v>37</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>250</v>
+        <v>112</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>251</v>
+        <v>113</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5825,22 +6126,22 @@
         <v>37</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>37</v>
@@ -5849,26 +6150,29 @@
         <v>37</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>37</v>
@@ -5880,15 +6184,17 @@
         <v>37</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>37</v>
@@ -5937,22 +6243,22 @@
         <v>37</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>37</v>
@@ -5961,19 +6267,22 @@
         <v>37</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5986,24 +6295,26 @@
         <v>37</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>37</v>
       </c>
@@ -6051,7 +6362,7 @@
         <v>37</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
@@ -6066,7 +6377,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>37</v>
@@ -6075,51 +6386,50 @@
         <v>37</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>37</v>
       </c>
@@ -6167,22 +6477,22 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>133</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>37</v>
@@ -6191,19 +6501,22 @@
         <v>37</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6222,13 +6535,13 @@
         <v>37</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6255,13 +6568,13 @@
         <v>37</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>37</v>
+        <v>292</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>37</v>
@@ -6279,7 +6592,7 @@
         <v>37</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6294,24 +6607,27 @@
         <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6334,13 +6650,13 @@
         <v>37</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6391,7 +6707,7 @@
         <v>37</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -6406,24 +6722,27 @@
         <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>37</v>
+        <v>297</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>37</v>
+        <v>298</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6434,7 +6753,7 @@
         <v>38</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>37</v>
@@ -6446,15 +6765,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>37</v>
@@ -6503,13 +6824,13 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>37</v>
@@ -6518,24 +6839,27 @@
         <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>37</v>
+        <v>275</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6543,13 +6867,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>45</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>37</v>
@@ -6558,13 +6882,13 @@
         <v>37</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6591,13 +6915,11 @@
         <v>37</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>37</v>
+        <v>305</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>37</v>
@@ -6615,7 +6937,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>124</v>
+        <v>302</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -6627,10 +6949,10 @@
         <v>37</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>37</v>
@@ -6639,19 +6961,22 @@
         <v>37</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>37</v>
+        <v>306</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>306</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6670,17 +6995,15 @@
         <v>37</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>92</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>37</v>
@@ -6729,7 +7052,7 @@
         <v>37</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>128</v>
+        <v>307</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -6741,10 +7064,10 @@
         <v>37</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>37</v>
@@ -6753,51 +7076,50 @@
         <v>37</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>37</v>
       </c>
@@ -6845,22 +7167,22 @@
         <v>37</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>37</v>
@@ -6869,26 +7191,29 @@
         <v>37</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>226</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>37</v>
@@ -6900,15 +7225,17 @@
         <v>37</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>268</v>
+        <v>92</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>37</v>
@@ -6957,22 +7284,22 @@
         <v>37</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>267</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>37</v>
@@ -6981,47 +7308,54 @@
         <v>37</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>37</v>
       </c>
@@ -7069,43 +7403,46 @@
         <v>37</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>270</v>
+        <v>187</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7124,13 +7461,13 @@
         <v>37</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7181,7 +7518,7 @@
         <v>37</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>45</v>
@@ -7205,15 +7542,18 @@
         <v>37</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7224,7 +7564,7 @@
         <v>38</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>37</v>
@@ -7236,13 +7576,13 @@
         <v>37</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7293,13 +7633,13 @@
         <v>37</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>37</v>
@@ -7311,21 +7651,24 @@
         <v>37</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7336,7 +7679,7 @@
         <v>38</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>37</v>
@@ -7348,13 +7691,13 @@
         <v>37</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>122</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>123</v>
+        <v>321</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7405,22 +7748,22 @@
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>124</v>
+        <v>319</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>37</v>
@@ -7429,26 +7772,29 @@
         <v>37</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>37</v>
@@ -7460,17 +7806,15 @@
         <v>37</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>37</v>
@@ -7519,22 +7863,22 @@
         <v>37</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>37</v>
@@ -7543,19 +7887,22 @@
         <v>37</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7568,26 +7915,24 @@
         <v>37</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>37</v>
       </c>
@@ -7635,7 +7980,7 @@
         <v>37</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -7650,7 +7995,7 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>37</v>
@@ -7659,47 +8004,54 @@
         <v>37</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>283</v>
+        <v>185</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>37</v>
       </c>
@@ -7747,22 +8099,22 @@
         <v>37</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>282</v>
+        <v>187</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>37</v>
@@ -7771,26 +8123,29 @@
         <v>37</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>37</v>
@@ -7802,13 +8157,13 @@
         <v>37</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>286</v>
+        <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7859,13 +8214,13 @@
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>37</v>
@@ -7883,15 +8238,18 @@
         <v>37</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7902,7 +8260,7 @@
         <v>38</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>37</v>
@@ -7914,13 +8272,13 @@
         <v>37</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7971,13 +8329,13 @@
         <v>37</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>37</v>
@@ -7989,21 +8347,24 @@
         <v>37</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8017,7 +8378,7 @@
         <v>45</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>37</v>
@@ -8026,18 +8387,16 @@
         <v>37</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>37</v>
       </c>
@@ -8085,10 +8444,10 @@
         <v>37</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>45</v>
@@ -8100,24 +8459,27 @@
         <v>57</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>297</v>
+        <v>37</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>298</v>
+        <v>37</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8128,7 +8490,7 @@
         <v>38</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>37</v>
@@ -8140,13 +8502,13 @@
         <v>37</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8197,13 +8559,13 @@
         <v>37</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>37</v>
@@ -8212,24 +8574,27 @@
         <v>57</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>303</v>
+        <v>37</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>304</v>
+        <v>37</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8240,7 +8605,7 @@
         <v>38</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>37</v>
@@ -8252,17 +8617,15 @@
         <v>37</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>306</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>307</v>
+        <v>112</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>37</v>
@@ -8311,50 +8674,53 @@
         <v>37</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>305</v>
+        <v>114</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>304</v>
+        <v>37</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>37</v>
@@ -8366,18 +8732,18 @@
         <v>37</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>312</v>
+        <v>91</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>313</v>
+        <v>92</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>37</v>
       </c>
@@ -8425,73 +8791,78 @@
         <v>37</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>316</v>
+        <v>115</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>37</v>
       </c>
@@ -8539,39 +8910,42 @@
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>322</v>
+        <v>88</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8579,10 +8953,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>37</v>
@@ -8594,13 +8968,13 @@
         <v>37</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8651,13 +9025,13 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>37</v>
@@ -8666,7 +9040,7 @@
         <v>57</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>327</v>
+        <v>37</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>37</v>
@@ -8675,15 +9049,18 @@
         <v>37</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8703,16 +9080,16 @@
         <v>37</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8763,7 +9140,7 @@
         <v>37</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>38</v>
@@ -8778,7 +9155,7 @@
         <v>57</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>37</v>
@@ -8787,15 +9164,18 @@
         <v>37</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8806,7 +9186,7 @@
         <v>38</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>37</v>
@@ -8818,13 +9198,13 @@
         <v>37</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>332</v>
+        <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8875,13 +9255,13 @@
         <v>37</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>37</v>
@@ -8901,9 +9281,940 @@
       <c r="AN66" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="AO66" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AO74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8913,7 +10224,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitterDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GENERATOR IMPLANT (file 698) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (#698) to ImplantableDevicePacemakerDevice</t>
   </si>
   <si>
     <t>Purpose</t>
